--- a/data/high.xlsx
+++ b/data/high.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="13.0" lowestEdited="13.0" rupBuild="0.1408"/>
+  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.3970"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
@@ -9,11 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="12180" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11340" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="high" sheetId="1" r:id="rId4"/>
   </x:sheets>
+  <x:externalReferences>
+    <x:externalReference r:id="rId5"/>
+  </x:externalReferences>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
@@ -21,223 +24,223 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <x:si>
+    <x:t>경기도 시흥시 금오로 103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-488-5333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-8708-2117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-489-8114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8084-8102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-5100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-496-2969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 금오로 640</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 승지로 107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-7150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-460-8900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-8400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-2610-4600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 상직길 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-5201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1525</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-2744</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 463</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-430-8226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-310-9000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국조리과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기자동차과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/ 11/ 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/ 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자디지털과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기스마트고등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-6100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복특+시간+순회+일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특1/시간제2/순회1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(고)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕신길로 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로487번길 54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은행고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve"> 학교설립별</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로 404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특1/시간제2/순회1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복특+시간+순회+일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-8400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-2744</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-430-8226</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-496-2969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 상직길 25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-489-8114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8084-8102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기스마트고등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-6100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-488-5333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-5201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1525</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 103</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화로 35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-2610-4600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 640</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4342</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-310-9000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-460-8900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 463</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행고길 85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-8708-2117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-7150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕신길로 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/ 11/ 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기자동차과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(고)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/ 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은행고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로487번길 54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자디지털과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국조리과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
   </x:si>
   <x:si>
     <x:t>특수/순회학급 배치 학생 수</x:t>
@@ -307,26 +310,11 @@
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="돋움"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="돋움"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
   </x:fonts>
   <x:fills count="2">
     <x:fill>
@@ -452,9 +440,692 @@
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
   </x:cellStyles>
-  <x:dxfs/>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:dxfs count="12">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf/>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffaebfea"/>
+          <x:bgColor rgb="ffaebfea"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
+          <x:bgColor rgb="ff94a5df"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:top style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:top>
+        <x:bottom style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
+          <x:bgColor rgb="ff6182d6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </x:dxfs>
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="0"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </x:tableStyle>
+    <x:tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </x:tableStyle>
+  </x:tableStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:externalBook r:id="rId1">
+    <x:sheetNames>
+      <x:sheetName val="&lt;총괄"/>
+      <x:sheetName val="특수학급 변동"/>
+      <x:sheetName val="영아"/>
+      <x:sheetName val="1_ 유치원"/>
+      <x:sheetName val="명단-유치원"/>
+      <x:sheetName val="2.초등"/>
+      <x:sheetName val="명단-초등학교"/>
+      <x:sheetName val="3.중등"/>
+      <x:sheetName val="명단-중학교"/>
+      <x:sheetName val="4.고등"/>
+      <x:sheetName val="명단-고등학교"/>
+      <x:sheetName val="영유아보육료"/>
+      <x:sheetName val="부결"/>
+      <x:sheetName val="취소"/>
+      <x:sheetName val="유예, 정원외 관리, 취학유예 등"/>
+      <x:sheetName val="전출"/>
+      <x:sheetName val="의료지원 필요 특수교육대상자"/>
+      <x:sheetName val="건강장애 원격수업 이용현황"/>
+      <x:sheetName val="치료사 치료지원"/>
+      <x:sheetName val="졸업자 명단"/>
+      <x:sheetName val="개교예정교"/>
+      <x:sheetName val="센터현황"/>
+      <x:sheetName val="2026. 9. 1.자 추가배치 신청"/>
+      <x:sheetName val="2026. 9. 1.자 추가배치 신청 (2)"/>
+      <x:sheetName val="특수교사"/>
+      <x:sheetName val="협력강사"/>
+      <x:sheetName val="특수교육지도사"/>
+      <x:sheetName val="사회복무요원"/>
+      <x:sheetName val="교내활동지원"/>
+      <x:sheetName val="학교내일자리·봉사"/>
+      <x:sheetName val="특수교육종일반"/>
+      <x:sheetName val="꿈이든카드제공기관"/>
+      <x:sheetName val="경기 특수학교 및 지원센터&gt;"/>
+      <x:sheetName val="학교급설치현황(유)"/>
+      <x:sheetName val="학교급설치현황(초)"/>
+      <x:sheetName val="학교급설치현황(중)"/>
+      <x:sheetName val="학교급설치현황(고)"/>
+      <x:sheetName val="구글지도 업로드용(유)"/>
+      <x:sheetName val="구글지도 업로드용 (초)"/>
+      <x:sheetName val="구글지도 업로드용 (중)"/>
+      <x:sheetName val="구글지도 업로드용 (고)"/>
+    </x:sheetNames>
+    <x:sheetDataSet>
+      <x:sheetData sheetId="0" refreshError="0"/>
+      <x:sheetData sheetId="1" refreshError="0"/>
+      <x:sheetData sheetId="2" refreshError="0"/>
+      <x:sheetData sheetId="3" refreshError="0"/>
+      <x:sheetData sheetId="4" refreshError="0"/>
+      <x:sheetData sheetId="5" refreshError="0"/>
+      <x:sheetData sheetId="6" refreshError="0"/>
+      <x:sheetData sheetId="7" refreshError="0"/>
+      <x:sheetData sheetId="8" refreshError="0"/>
+      <x:sheetData sheetId="9" refreshError="0"/>
+      <x:sheetData sheetId="10" refreshError="0"/>
+      <x:sheetData sheetId="11" refreshError="0"/>
+      <x:sheetData sheetId="12" refreshError="0"/>
+      <x:sheetData sheetId="13" refreshError="0"/>
+      <x:sheetData sheetId="14" refreshError="0"/>
+      <x:sheetData sheetId="15" refreshError="0"/>
+      <x:sheetData sheetId="16" refreshError="0"/>
+      <x:sheetData sheetId="17" refreshError="0"/>
+      <x:sheetData sheetId="18" refreshError="0"/>
+      <x:sheetData sheetId="19" refreshError="0"/>
+      <x:sheetData sheetId="20" refreshError="0"/>
+      <x:sheetData sheetId="21" refreshError="0"/>
+      <x:sheetData sheetId="22" refreshError="0"/>
+      <x:sheetData sheetId="23" refreshError="0"/>
+      <x:sheetData sheetId="24" refreshError="0"/>
+      <x:sheetData sheetId="25" refreshError="0"/>
+      <x:sheetData sheetId="26" refreshError="0"/>
+      <x:sheetData sheetId="27" refreshError="0"/>
+      <x:sheetData sheetId="28" refreshError="0"/>
+      <x:sheetData sheetId="29" refreshError="0"/>
+      <x:sheetData sheetId="30" refreshError="0"/>
+      <x:sheetData sheetId="31" refreshError="0"/>
+      <x:sheetData sheetId="32" refreshError="0"/>
+      <x:sheetData sheetId="33" refreshError="0"/>
+      <x:sheetData sheetId="34" refreshError="0"/>
+      <x:sheetData sheetId="35" refreshError="0"/>
+      <x:sheetData sheetId="36" refreshError="0">
+        <x:row r="7">
+          <x:cell r="I7">
+            <x:v>11</x:v>
+          </x:cell>
+          <x:cell r="L7">
+            <x:v>4</x:v>
+          </x:cell>
+          <x:cell r="Q7">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="8">
+          <x:cell r="I8">
+            <x:v>4</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="9">
+          <x:cell r="E9">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I9">
+            <x:v>14</x:v>
+          </x:cell>
+          <x:cell r="Q9">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="10">
+          <x:cell r="E10">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I10">
+            <x:v>22</x:v>
+          </x:cell>
+          <x:cell r="K10">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="L10">
+            <x:v>4</x:v>
+          </x:cell>
+          <x:cell r="Q10">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="11">
+          <x:cell r="E11">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I11">
+            <x:v>9</x:v>
+          </x:cell>
+          <x:cell r="Q11">
+            <x:v>3</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="12">
+          <x:cell r="E12">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I12">
+            <x:v>14</x:v>
+          </x:cell>
+          <x:cell r="Q12">
+            <x:v>8</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="13">
+          <x:cell r="E13">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I13">
+            <x:v>22</x:v>
+          </x:cell>
+          <x:cell r="Q13">
+            <x:v>6</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="14">
+          <x:cell r="E14">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="I14">
+            <x:v>7</x:v>
+          </x:cell>
+          <x:cell r="Q14">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="15">
+          <x:cell r="E15">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I15">
+            <x:v>14</x:v>
+          </x:cell>
+          <x:cell r="Q15">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="16">
+          <x:cell r="E16">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I16">
+            <x:v>12</x:v>
+          </x:cell>
+          <x:cell r="Q16">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="17">
+          <x:cell r="E17">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="I17">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="Q17">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="18">
+          <x:cell r="E18">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I18">
+            <x:v>20</x:v>
+          </x:cell>
+          <x:cell r="Q18">
+            <x:v>0</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="19">
+          <x:cell r="E19">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I19">
+            <x:v>20</x:v>
+          </x:cell>
+          <x:cell r="Q19">
+            <x:v>4</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="20">
+          <x:cell r="E20">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I20">
+            <x:v>12</x:v>
+          </x:cell>
+          <x:cell r="Q20">
+            <x:v>5</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="21">
+          <x:cell r="E21">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I21">
+            <x:v>15</x:v>
+          </x:cell>
+          <x:cell r="Q21">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="22">
+          <x:cell r="E22"/>
+          <x:cell r="I22"/>
+          <x:cell r="Q22">
+            <x:v>3</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="23">
+          <x:cell r="E23"/>
+          <x:cell r="I23"/>
+          <x:cell r="Q23">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="24">
+          <x:cell r="E24"/>
+          <x:cell r="I24"/>
+          <x:cell r="Q24">
+            <x:v>0</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="25">
+          <x:cell r="Q25">
+            <x:v>0</x:v>
+          </x:cell>
+        </x:row>
+      </x:sheetData>
+      <x:sheetData sheetId="37" refreshError="0"/>
+      <x:sheetData sheetId="38" refreshError="0"/>
+      <x:sheetData sheetId="39" refreshError="0"/>
+      <x:sheetData sheetId="40" refreshError="0"/>
+    </x:sheetDataSet>
+  </x:externalBook>
+</x:externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -779,23 +1450,24 @@
     <x:col min="5" max="5" width="15.69140625" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="24.55078125" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="21.63671875" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="11" width="13.03125" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" t="s">
-        <x:v>1</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>0</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>3</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>2</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F1" t="s">
         <x:v>73</x:v>
@@ -804,45 +1476,47 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>4</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="str">
+        <x:f>'[1]학교급설치현황(고)'!I8&amp;"/ "&amp;'[1]학교급설치현황(고)'!I7&amp;"/ "&amp;'[1]학교급설치현황(고)'!L7</x:f>
+        <x:v>4/ 11/ 4</x:v>
       </x:c>
       <x:c r="G2" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q7</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J2" s="6">
         <x:v>37.343459867978297</x:v>
@@ -853,28 +1527,31 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E3" s="7">
+        <x:f>'[1]학교급설치현황(고)'!E24</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="7">
+        <x:f>'[1]학교급설치현황(고)'!I24</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="8">
+        <x:f>'[1]학교급설치현황(고)'!Q24</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="6">
@@ -886,28 +1563,31 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E9</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I9</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q9</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="6">
@@ -919,16 +1599,16 @@
     </x:row>
     <x:row r="5" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="7">
         <x:v>0</x:v>
@@ -937,10 +1617,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="8">
+        <x:f>'[1]학교급설치현황(고)'!Q25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="6">
@@ -952,31 +1633,34 @@
     </x:row>
     <x:row r="6" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E6" s="10" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="str">
+        <x:f>'[1]학교급설치현황(고)'!E10&amp;"/ "&amp;'[1]학교급설치현황(고)'!K10</x:f>
+        <x:v>3/ 1</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:f>'[1]학교급설치현황(고)'!I10&amp;"/ "&amp;'[1]학교급설치현황(고)'!L10</x:f>
+        <x:v>22/ 4</x:v>
       </x:c>
       <x:c r="G6" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q10</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J6" s="6">
         <x:v>37.349803420991499</x:v>
@@ -987,28 +1671,31 @@
     </x:row>
     <x:row r="7" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A7" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E11</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I11</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="G7" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q11</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="6">
@@ -1020,28 +1707,31 @@
     </x:row>
     <x:row r="8" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E8" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E12</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I12</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q12</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="6">
@@ -1053,28 +1743,31 @@
     </x:row>
     <x:row r="9" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E13</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I13</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="G9" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q13</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="6">
@@ -1086,28 +1779,31 @@
     </x:row>
     <x:row r="10" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E14</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I14</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q14</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="6">
@@ -1119,28 +1815,31 @@
     </x:row>
     <x:row r="11" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I15</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="6">
@@ -1152,28 +1851,31 @@
     </x:row>
     <x:row r="12" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E12" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E16</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F12" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I16</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="G12" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q16</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="6">
@@ -1185,28 +1887,31 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E13" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="6">
@@ -1218,28 +1923,31 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E14" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E18</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I18</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="8">
+        <x:f>'[1]학교급설치현황(고)'!Q18</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="6">
@@ -1251,28 +1959,31 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A15" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E15" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E19</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I19</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q19</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="6">
@@ -1284,28 +1995,31 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E16" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E20</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F16" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I20</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="G16" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q20</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="H16" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I16" s="5"/>
       <x:c r="J16" s="6">
@@ -1317,28 +2031,31 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E17" s="7">
+        <x:f>'[1]학교급설치현황(고)'!E22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="7">
+        <x:f>'[1]학교급설치현황(고)'!I22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G17" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q22</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I17" s="5"/>
       <x:c r="J17" s="6">
@@ -1350,28 +2067,31 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="7">
+        <x:f>'[1]학교급설치현황(고)'!E23</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="7">
+        <x:f>'[1]학교급설치현황(고)'!I23</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G18" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q23</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I18" s="5"/>
       <x:c r="J18" s="6">
@@ -1383,28 +2103,31 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E19" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E21</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F19" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I21</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q21</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I19" s="5"/>
       <x:c r="J19" s="6">
@@ -1417,6 +2140,5 @@
   </x:sheetData>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
 </file>
--- a/data/high.xlsx
+++ b/data/high.xlsx
@@ -14,9 +14,6 @@
   <x:sheets>
     <x:sheet name="high" sheetId="1" r:id="rId4"/>
   </x:sheets>
-  <x:externalReferences>
-    <x:externalReference r:id="rId5"/>
-  </x:externalReferences>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
@@ -843,291 +840,6 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:externalBook r:id="rId1">
-    <x:sheetNames>
-      <x:sheetName val="&lt;총괄"/>
-      <x:sheetName val="특수학급 변동"/>
-      <x:sheetName val="영아"/>
-      <x:sheetName val="1_ 유치원"/>
-      <x:sheetName val="명단-유치원"/>
-      <x:sheetName val="2.초등"/>
-      <x:sheetName val="명단-초등학교"/>
-      <x:sheetName val="3.중등"/>
-      <x:sheetName val="명단-중학교"/>
-      <x:sheetName val="4.고등"/>
-      <x:sheetName val="명단-고등학교"/>
-      <x:sheetName val="영유아보육료"/>
-      <x:sheetName val="부결"/>
-      <x:sheetName val="취소"/>
-      <x:sheetName val="유예, 정원외 관리, 취학유예 등"/>
-      <x:sheetName val="전출"/>
-      <x:sheetName val="의료지원 필요 특수교육대상자"/>
-      <x:sheetName val="건강장애 원격수업 이용현황"/>
-      <x:sheetName val="치료사 치료지원"/>
-      <x:sheetName val="졸업자 명단"/>
-      <x:sheetName val="개교예정교"/>
-      <x:sheetName val="센터현황"/>
-      <x:sheetName val="2026. 9. 1.자 추가배치 신청"/>
-      <x:sheetName val="2026. 9. 1.자 추가배치 신청 (2)"/>
-      <x:sheetName val="특수교사"/>
-      <x:sheetName val="협력강사"/>
-      <x:sheetName val="특수교육지도사"/>
-      <x:sheetName val="사회복무요원"/>
-      <x:sheetName val="교내활동지원"/>
-      <x:sheetName val="학교내일자리·봉사"/>
-      <x:sheetName val="특수교육종일반"/>
-      <x:sheetName val="꿈이든카드제공기관"/>
-      <x:sheetName val="경기 특수학교 및 지원센터&gt;"/>
-      <x:sheetName val="학교급설치현황(유)"/>
-      <x:sheetName val="학교급설치현황(초)"/>
-      <x:sheetName val="학교급설치현황(중)"/>
-      <x:sheetName val="학교급설치현황(고)"/>
-      <x:sheetName val="구글지도 업로드용(유)"/>
-      <x:sheetName val="구글지도 업로드용 (초)"/>
-      <x:sheetName val="구글지도 업로드용 (중)"/>
-      <x:sheetName val="구글지도 업로드용 (고)"/>
-    </x:sheetNames>
-    <x:sheetDataSet>
-      <x:sheetData sheetId="0" refreshError="0"/>
-      <x:sheetData sheetId="1" refreshError="0"/>
-      <x:sheetData sheetId="2" refreshError="0"/>
-      <x:sheetData sheetId="3" refreshError="0"/>
-      <x:sheetData sheetId="4" refreshError="0"/>
-      <x:sheetData sheetId="5" refreshError="0"/>
-      <x:sheetData sheetId="6" refreshError="0"/>
-      <x:sheetData sheetId="7" refreshError="0"/>
-      <x:sheetData sheetId="8" refreshError="0"/>
-      <x:sheetData sheetId="9" refreshError="0"/>
-      <x:sheetData sheetId="10" refreshError="0"/>
-      <x:sheetData sheetId="11" refreshError="0"/>
-      <x:sheetData sheetId="12" refreshError="0"/>
-      <x:sheetData sheetId="13" refreshError="0"/>
-      <x:sheetData sheetId="14" refreshError="0"/>
-      <x:sheetData sheetId="15" refreshError="0"/>
-      <x:sheetData sheetId="16" refreshError="0"/>
-      <x:sheetData sheetId="17" refreshError="0"/>
-      <x:sheetData sheetId="18" refreshError="0"/>
-      <x:sheetData sheetId="19" refreshError="0"/>
-      <x:sheetData sheetId="20" refreshError="0"/>
-      <x:sheetData sheetId="21" refreshError="0"/>
-      <x:sheetData sheetId="22" refreshError="0"/>
-      <x:sheetData sheetId="23" refreshError="0"/>
-      <x:sheetData sheetId="24" refreshError="0"/>
-      <x:sheetData sheetId="25" refreshError="0"/>
-      <x:sheetData sheetId="26" refreshError="0"/>
-      <x:sheetData sheetId="27" refreshError="0"/>
-      <x:sheetData sheetId="28" refreshError="0"/>
-      <x:sheetData sheetId="29" refreshError="0"/>
-      <x:sheetData sheetId="30" refreshError="0"/>
-      <x:sheetData sheetId="31" refreshError="0"/>
-      <x:sheetData sheetId="32" refreshError="0"/>
-      <x:sheetData sheetId="33" refreshError="0"/>
-      <x:sheetData sheetId="34" refreshError="0"/>
-      <x:sheetData sheetId="35" refreshError="0"/>
-      <x:sheetData sheetId="36" refreshError="0">
-        <x:row r="7">
-          <x:cell r="I7">
-            <x:v>11</x:v>
-          </x:cell>
-          <x:cell r="L7">
-            <x:v>4</x:v>
-          </x:cell>
-          <x:cell r="Q7">
-            <x:v>1</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="8">
-          <x:cell r="I8">
-            <x:v>4</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="9">
-          <x:cell r="E9">
-            <x:v>2</x:v>
-          </x:cell>
-          <x:cell r="I9">
-            <x:v>14</x:v>
-          </x:cell>
-          <x:cell r="Q9">
-            <x:v>2</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="10">
-          <x:cell r="E10">
-            <x:v>3</x:v>
-          </x:cell>
-          <x:cell r="I10">
-            <x:v>22</x:v>
-          </x:cell>
-          <x:cell r="K10">
-            <x:v>1</x:v>
-          </x:cell>
-          <x:cell r="L10">
-            <x:v>4</x:v>
-          </x:cell>
-          <x:cell r="Q10">
-            <x:v>2</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="11">
-          <x:cell r="E11">
-            <x:v>2</x:v>
-          </x:cell>
-          <x:cell r="I11">
-            <x:v>9</x:v>
-          </x:cell>
-          <x:cell r="Q11">
-            <x:v>3</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="12">
-          <x:cell r="E12">
-            <x:v>2</x:v>
-          </x:cell>
-          <x:cell r="I12">
-            <x:v>14</x:v>
-          </x:cell>
-          <x:cell r="Q12">
-            <x:v>8</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="13">
-          <x:cell r="E13">
-            <x:v>3</x:v>
-          </x:cell>
-          <x:cell r="I13">
-            <x:v>22</x:v>
-          </x:cell>
-          <x:cell r="Q13">
-            <x:v>6</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="14">
-          <x:cell r="E14">
-            <x:v>1</x:v>
-          </x:cell>
-          <x:cell r="I14">
-            <x:v>7</x:v>
-          </x:cell>
-          <x:cell r="Q14">
-            <x:v>2</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="15">
-          <x:cell r="E15">
-            <x:v>2</x:v>
-          </x:cell>
-          <x:cell r="I15">
-            <x:v>14</x:v>
-          </x:cell>
-          <x:cell r="Q15">
-            <x:v>2</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="16">
-          <x:cell r="E16">
-            <x:v>2</x:v>
-          </x:cell>
-          <x:cell r="I16">
-            <x:v>12</x:v>
-          </x:cell>
-          <x:cell r="Q16">
-            <x:v>2</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="17">
-          <x:cell r="E17">
-            <x:v>1</x:v>
-          </x:cell>
-          <x:cell r="I17">
-            <x:v>1</x:v>
-          </x:cell>
-          <x:cell r="Q17">
-            <x:v>1</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="18">
-          <x:cell r="E18">
-            <x:v>3</x:v>
-          </x:cell>
-          <x:cell r="I18">
-            <x:v>20</x:v>
-          </x:cell>
-          <x:cell r="Q18">
-            <x:v>0</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="19">
-          <x:cell r="E19">
-            <x:v>3</x:v>
-          </x:cell>
-          <x:cell r="I19">
-            <x:v>20</x:v>
-          </x:cell>
-          <x:cell r="Q19">
-            <x:v>4</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="20">
-          <x:cell r="E20">
-            <x:v>2</x:v>
-          </x:cell>
-          <x:cell r="I20">
-            <x:v>12</x:v>
-          </x:cell>
-          <x:cell r="Q20">
-            <x:v>5</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="21">
-          <x:cell r="E21">
-            <x:v>2</x:v>
-          </x:cell>
-          <x:cell r="I21">
-            <x:v>15</x:v>
-          </x:cell>
-          <x:cell r="Q21">
-            <x:v>1</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="22">
-          <x:cell r="E22"/>
-          <x:cell r="I22"/>
-          <x:cell r="Q22">
-            <x:v>3</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="23">
-          <x:cell r="E23"/>
-          <x:cell r="I23"/>
-          <x:cell r="Q23">
-            <x:v>1</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="24">
-          <x:cell r="E24"/>
-          <x:cell r="I24"/>
-          <x:cell r="Q24">
-            <x:v>0</x:v>
-          </x:cell>
-        </x:row>
-        <x:row r="25">
-          <x:cell r="Q25">
-            <x:v>0</x:v>
-          </x:cell>
-        </x:row>
-      </x:sheetData>
-      <x:sheetData sheetId="37" refreshError="0"/>
-      <x:sheetData sheetId="38" refreshError="0"/>
-      <x:sheetData sheetId="39" refreshError="0"/>
-      <x:sheetData sheetId="40" refreshError="0"/>
-    </x:sheetDataSet>
-  </x:externalBook>
-</x:externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
   <a:themeElements>
@@ -1504,12 +1216,10 @@
       <x:c r="E2" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="str">
-        <x:f>'[1]학교급설치현황(고)'!I8&amp;"/ "&amp;'[1]학교급설치현황(고)'!I7&amp;"/ "&amp;'[1]학교급설치현황(고)'!L7</x:f>
-        <x:v>4/ 11/ 4</x:v>
+      <x:c r="F2" s="2" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q7</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
@@ -1539,15 +1249,12 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E3" s="7">
-        <x:f>'[1]학교급설치현황(고)'!E24</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="7">
-        <x:f>'[1]학교급설치현황(고)'!I24</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="8">
-        <x:f>'[1]학교급설치현황(고)'!Q24</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="4" t="s">
@@ -1575,15 +1282,12 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E9</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I9</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q9</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
@@ -1617,7 +1321,6 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="8">
-        <x:f>'[1]학교급설치현황(고)'!Q25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
@@ -1644,16 +1347,13 @@
       <x:c r="D6" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E6" s="10" t="str">
-        <x:f>'[1]학교급설치현황(고)'!E10&amp;"/ "&amp;'[1]학교급설치현황(고)'!K10</x:f>
-        <x:v>3/ 1</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="str">
-        <x:f>'[1]학교급설치현황(고)'!I10&amp;"/ "&amp;'[1]학교급설치현황(고)'!L10</x:f>
-        <x:v>22/ 4</x:v>
+      <x:c r="E6" s="10" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G6" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q10</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
@@ -1683,15 +1383,12 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E11</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I11</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="G7" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q11</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
@@ -1719,15 +1416,12 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E8" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E12</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I12</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q12</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
@@ -1755,15 +1449,12 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E13</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I13</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="G9" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q13</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
@@ -1791,15 +1482,12 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E14</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I14</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q14</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
@@ -1827,15 +1515,12 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I15</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
@@ -1863,15 +1548,12 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E12" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E16</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F12" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I16</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="G12" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q16</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
@@ -1899,15 +1581,12 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E13" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
@@ -1935,15 +1614,12 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E14" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E18</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I18</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="8">
-        <x:f>'[1]학교급설치현황(고)'!Q18</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
@@ -1971,15 +1647,12 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E15" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E19</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I19</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q19</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
@@ -2007,15 +1680,12 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E16" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E20</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F16" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I20</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="G16" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q20</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="H16" s="4" t="s">
@@ -2043,15 +1713,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E17" s="7">
-        <x:f>'[1]학교급설치현황(고)'!E22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="7">
-        <x:f>'[1]학교급설치현황(고)'!I22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G17" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q22</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="4" t="s">
@@ -2079,15 +1746,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="7">
-        <x:f>'[1]학교급설치현황(고)'!E23</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="7">
-        <x:f>'[1]학교급설치현황(고)'!I23</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G18" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q23</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="4" t="s">
@@ -2115,15 +1779,12 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E19" s="9">
-        <x:f>'[1]학교급설치현황(고)'!E21</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F19" s="3">
-        <x:f>'[1]학교급설치현황(고)'!I21</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="3">
-        <x:f>'[1]학교급설치현황(고)'!Q21</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="4" t="s">

--- a/data/high.xlsx
+++ b/data/high.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V5 -\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V5+Q&amp;A+학구 -\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -14,6 +14,9 @@
   <x:sheets>
     <x:sheet name="high" sheetId="1" r:id="rId4"/>
   </x:sheets>
+  <x:externalReferences>
+    <x:externalReference r:id="rId5"/>
+  </x:externalReferences>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
@@ -21,229 +24,229 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <x:si>
+    <x:t>함현고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은행고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/ 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-8708-2117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(고)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국조리과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자디지털과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/ 11/ 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기자동차과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로487번길 54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕신길로 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 금오로 103</x:t>
   </x:si>
   <x:si>
+    <x:t>경기스마트고등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-488-5333</x:t>
   </x:si>
   <x:si>
-    <x:t>070-8708-2117</x:t>
+    <x:t>경기도 시흥시 역전로 463</x:t>
   </x:si>
   <x:si>
     <x:t>031-489-8114</x:t>
   </x:si>
   <x:si>
+    <x:t>경기도 시흥시 금오로 640</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-496-2969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특1/시간제2/순회1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-5201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1525</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-430-8226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 상직길 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-6100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-310-9000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-8400</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-8084-8102</x:t>
   </x:si>
   <x:si>
+    <x:t>경기도 시흥시 승지로 107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-460-8900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-2610-4600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-7150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-2744</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복특+시간+순회+일반)</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-363-5100</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 매화로 35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-496-2969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 640</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-7150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4342</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-460-8900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-8400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-2610-4600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 상직길 25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-5201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1525</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8365</x:t>
-  </x:si>
-  <x:si>
     <x:t>경기도 시흥시 은행고길 85</x:t>
   </x:si>
   <x:si>
-    <x:t>031-317-2744</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 463</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-430-8226</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-310-9000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국조리과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기자동차과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/ 11/ 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/ 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자디지털과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기스마트고등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-6100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복특+시간+순회+일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특1/시간제2/순회1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(고)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕신길로 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로 404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로487번길 54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은행고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
+    <x:t>일반학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
     <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -840,6 +843,293 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:externalBook r:id="rId1">
+    <x:sheetNames>
+      <x:sheetName val="목차"/>
+      <x:sheetName val="&lt;총괄"/>
+      <x:sheetName val="특수학급 변동"/>
+      <x:sheetName val="영아"/>
+      <x:sheetName val="1_ 유치원"/>
+      <x:sheetName val="명단-유치원"/>
+      <x:sheetName val="2.초등"/>
+      <x:sheetName val="명단-초등학교"/>
+      <x:sheetName val="3.중등"/>
+      <x:sheetName val="명단-중학교"/>
+      <x:sheetName val="4.고등"/>
+      <x:sheetName val="명단-고등학교"/>
+      <x:sheetName val="영유아보육료"/>
+      <x:sheetName val="부결"/>
+      <x:sheetName val="취소"/>
+      <x:sheetName val="유예, 정원외 관리, 취학유예 등"/>
+      <x:sheetName val="전출"/>
+      <x:sheetName val="의료지원 필요 특수교육대상자"/>
+      <x:sheetName val="건강장애 원격수업 이용현황"/>
+      <x:sheetName val="치료사 치료지원"/>
+      <x:sheetName val="졸업자 명단"/>
+      <x:sheetName val="개교예정교"/>
+      <x:sheetName val="센터현황"/>
+      <x:sheetName val="2026. 9. 1.자 추가교원 배치 신청교"/>
+      <x:sheetName val="특수교사"/>
+      <x:sheetName val="협력강사"/>
+      <x:sheetName val="순회교육현황"/>
+      <x:sheetName val="특수교육지도사"/>
+      <x:sheetName val="사회복무요원"/>
+      <x:sheetName val="교내활동지원"/>
+      <x:sheetName val="학교내일자리·봉사"/>
+      <x:sheetName val="특수교육종일반"/>
+      <x:sheetName val="꿈이든카드제공기관"/>
+      <x:sheetName val="경기 특수학교 및 지원센터&gt;"/>
+      <x:sheetName val="학교급설치현황(유)"/>
+      <x:sheetName val="학교급설치현황(초)"/>
+      <x:sheetName val="학교급설치현황(중)"/>
+      <x:sheetName val="학교급설치현황(고)"/>
+      <x:sheetName val="구글지도 업로드용(유)"/>
+      <x:sheetName val="구글지도 업로드용 (초)"/>
+      <x:sheetName val="구글지도 업로드용 (중)"/>
+      <x:sheetName val="구글지도 업로드용 (고)"/>
+    </x:sheetNames>
+    <x:sheetDataSet>
+      <x:sheetData sheetId="0" refreshError="0"/>
+      <x:sheetData sheetId="1" refreshError="0"/>
+      <x:sheetData sheetId="2" refreshError="0"/>
+      <x:sheetData sheetId="3" refreshError="0"/>
+      <x:sheetData sheetId="4" refreshError="0"/>
+      <x:sheetData sheetId="5" refreshError="0"/>
+      <x:sheetData sheetId="6" refreshError="0"/>
+      <x:sheetData sheetId="7" refreshError="0"/>
+      <x:sheetData sheetId="8" refreshError="0"/>
+      <x:sheetData sheetId="9" refreshError="0"/>
+      <x:sheetData sheetId="10" refreshError="0"/>
+      <x:sheetData sheetId="11" refreshError="0"/>
+      <x:sheetData sheetId="12" refreshError="0"/>
+      <x:sheetData sheetId="13" refreshError="0"/>
+      <x:sheetData sheetId="14" refreshError="0"/>
+      <x:sheetData sheetId="15" refreshError="0"/>
+      <x:sheetData sheetId="16" refreshError="0"/>
+      <x:sheetData sheetId="17" refreshError="0"/>
+      <x:sheetData sheetId="18" refreshError="0"/>
+      <x:sheetData sheetId="19" refreshError="0"/>
+      <x:sheetData sheetId="20" refreshError="0"/>
+      <x:sheetData sheetId="21" refreshError="0"/>
+      <x:sheetData sheetId="22" refreshError="0"/>
+      <x:sheetData sheetId="23" refreshError="0"/>
+      <x:sheetData sheetId="24" refreshError="0"/>
+      <x:sheetData sheetId="25" refreshError="0"/>
+      <x:sheetData sheetId="26" refreshError="0"/>
+      <x:sheetData sheetId="27" refreshError="0"/>
+      <x:sheetData sheetId="28" refreshError="0"/>
+      <x:sheetData sheetId="29" refreshError="0"/>
+      <x:sheetData sheetId="30" refreshError="0"/>
+      <x:sheetData sheetId="31" refreshError="0"/>
+      <x:sheetData sheetId="32" refreshError="0"/>
+      <x:sheetData sheetId="33" refreshError="0"/>
+      <x:sheetData sheetId="34" refreshError="0"/>
+      <x:sheetData sheetId="35" refreshError="0"/>
+      <x:sheetData sheetId="36" refreshError="0"/>
+      <x:sheetData sheetId="37" refreshError="0">
+        <x:row r="7">
+          <x:cell r="I7">
+            <x:v>11</x:v>
+          </x:cell>
+          <x:cell r="L7">
+            <x:v>4</x:v>
+          </x:cell>
+          <x:cell r="Q7">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="8">
+          <x:cell r="I8">
+            <x:v>4</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="9">
+          <x:cell r="E9">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I9">
+            <x:v>14</x:v>
+          </x:cell>
+          <x:cell r="Q9">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="10">
+          <x:cell r="E10">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I10">
+            <x:v>22</x:v>
+          </x:cell>
+          <x:cell r="K10">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="L10">
+            <x:v>4</x:v>
+          </x:cell>
+          <x:cell r="Q10">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="11">
+          <x:cell r="E11">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I11">
+            <x:v>9</x:v>
+          </x:cell>
+          <x:cell r="Q11">
+            <x:v>3</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="12">
+          <x:cell r="E12">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I12">
+            <x:v>14</x:v>
+          </x:cell>
+          <x:cell r="Q12">
+            <x:v>8</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="13">
+          <x:cell r="E13">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I13">
+            <x:v>22</x:v>
+          </x:cell>
+          <x:cell r="Q13">
+            <x:v>6</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="14">
+          <x:cell r="E14">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="I14">
+            <x:v>6</x:v>
+          </x:cell>
+          <x:cell r="Q14">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="15">
+          <x:cell r="E15">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I15">
+            <x:v>14</x:v>
+          </x:cell>
+          <x:cell r="Q15">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="16">
+          <x:cell r="E16">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I16">
+            <x:v>12</x:v>
+          </x:cell>
+          <x:cell r="Q16">
+            <x:v>2</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="17">
+          <x:cell r="E17">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="I17">
+            <x:v>1</x:v>
+          </x:cell>
+          <x:cell r="Q17">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="18">
+          <x:cell r="E18">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I18">
+            <x:v>20</x:v>
+          </x:cell>
+          <x:cell r="Q18">
+            <x:v>0</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="19">
+          <x:cell r="E19">
+            <x:v>3</x:v>
+          </x:cell>
+          <x:cell r="I19">
+            <x:v>20</x:v>
+          </x:cell>
+          <x:cell r="Q19">
+            <x:v>4</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="20">
+          <x:cell r="E20">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I20">
+            <x:v>12</x:v>
+          </x:cell>
+          <x:cell r="Q20">
+            <x:v>5</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="21">
+          <x:cell r="E21">
+            <x:v>2</x:v>
+          </x:cell>
+          <x:cell r="I21">
+            <x:v>15</x:v>
+          </x:cell>
+          <x:cell r="Q21">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="22">
+          <x:cell r="E22"/>
+          <x:cell r="I22"/>
+          <x:cell r="Q22">
+            <x:v>3</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="23">
+          <x:cell r="E23"/>
+          <x:cell r="I23"/>
+          <x:cell r="Q23">
+            <x:v>1</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="24">
+          <x:cell r="E24"/>
+          <x:cell r="I24"/>
+          <x:cell r="Q24">
+            <x:v>0</x:v>
+          </x:cell>
+        </x:row>
+        <x:row r="25">
+          <x:cell r="Q25">
+            <x:v>0</x:v>
+          </x:cell>
+        </x:row>
+      </x:sheetData>
+      <x:sheetData sheetId="38" refreshError="0"/>
+      <x:sheetData sheetId="39" refreshError="0"/>
+      <x:sheetData sheetId="40" refreshError="0"/>
+      <x:sheetData sheetId="41" refreshError="0"/>
+    </x:sheetDataSet>
+  </x:externalBook>
+</x:externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
   <a:themeElements>
@@ -1167,66 +1457,68 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" t="s">
-        <x:v>72</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>71</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>53</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G1" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="H1" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>46</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="str">
+        <x:f>'[1]학교급설치현황(고)'!I8&amp;"/ "&amp;'[1]학교급설치현황(고)'!I7&amp;"/ "&amp;'[1]학교급설치현황(고)'!L7</x:f>
+        <x:v>4/ 11/ 4</x:v>
       </x:c>
       <x:c r="G2" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q7</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J2" s="6">
         <x:v>37.343459867978297</x:v>
@@ -1237,28 +1529,31 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E3" s="7">
+        <x:f>'[1]학교급설치현황(고)'!E24</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E3" s="7">
+      <x:c r="F3" s="7">
+        <x:f>'[1]학교급설치현황(고)'!I24</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F3" s="7">
+      <x:c r="G3" s="8">
+        <x:f>'[1]학교급설치현황(고)'!Q24</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G3" s="8">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="H3" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="6">
@@ -1270,28 +1565,31 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A4" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E4" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E9</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I9</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q9</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="6">
@@ -1303,16 +1601,16 @@
     </x:row>
     <x:row r="5" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E5" s="7">
         <x:v>0</x:v>
@@ -1321,10 +1619,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="8">
+        <x:f>'[1]학교급설치현황(고)'!Q25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="6">
@@ -1336,31 +1635,34 @@
     </x:row>
     <x:row r="6" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="10" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="str">
+        <x:f>'[1]학교급설치현황(고)'!E10&amp;"/ "&amp;'[1]학교급설치현황(고)'!K10</x:f>
+        <x:v>3/ 1</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:f>'[1]학교급설치현황(고)'!I10&amp;"/ "&amp;'[1]학교급설치현황(고)'!L10</x:f>
+        <x:v>22/ 4</x:v>
       </x:c>
       <x:c r="G6" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q10</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J6" s="6">
         <x:v>37.349803420991499</x:v>
@@ -1371,28 +1673,31 @@
     </x:row>
     <x:row r="7" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A7" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E7" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E11</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I11</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="G7" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q11</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="6">
@@ -1404,28 +1709,31 @@
     </x:row>
     <x:row r="8" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E8" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E12</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I12</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q12</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="6">
@@ -1437,28 +1745,31 @@
     </x:row>
     <x:row r="9" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A9" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E9" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E13</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I13</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="G9" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q13</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="6">
@@ -1470,28 +1781,31 @@
     </x:row>
     <x:row r="10" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E10" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E14</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I14</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G10" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q14</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H10" s="4" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E10" s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="3">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G10" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H10" s="4" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="6">
@@ -1503,28 +1817,31 @@
     </x:row>
     <x:row r="11" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E11" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I15</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="6">
@@ -1536,28 +1853,31 @@
     </x:row>
     <x:row r="12" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E12" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E16</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F12" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I16</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="G12" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q16</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="6">
@@ -1569,28 +1889,31 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q17</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="6">
@@ -1602,28 +1925,31 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E14" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E18</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I18</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="8">
+        <x:f>'[1]학교급설치현황(고)'!Q18</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="6">
@@ -1635,28 +1961,31 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E15" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E19</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F15" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I19</x:f>
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E15" s="9">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F15" s="3">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="G15" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q19</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="6">
@@ -1668,28 +1997,31 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E16" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E20</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F16" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I20</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="G16" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q20</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="H16" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I16" s="5"/>
       <x:c r="J16" s="6">
@@ -1701,28 +2033,31 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E17" s="7">
+        <x:f>'[1]학교급설치현황(고)'!E22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="7">
+        <x:f>'[1]학교급설치현황(고)'!I22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G17" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q22</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I17" s="5"/>
       <x:c r="J17" s="6">
@@ -1734,28 +2069,31 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E18" s="7">
+        <x:f>'[1]학교급설치현황(고)'!E23</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="7">
+        <x:f>'[1]학교급설치현황(고)'!I23</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G18" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q23</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I18" s="5"/>
       <x:c r="J18" s="6">
@@ -1767,28 +2105,31 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E19" s="9">
+        <x:f>'[1]학교급설치현황(고)'!E21</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F19" s="3">
+        <x:f>'[1]학교급설치현황(고)'!I21</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="3">
+        <x:f>'[1]학교급설치현황(고)'!Q21</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I19" s="5"/>
       <x:c r="J19" s="6">
